--- a/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_9_44.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_9_44.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3762670.894734366</v>
+        <v>3798999.849469504</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13275569.19337385</v>
+        <v>13279501.51514058</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13275569.19337385</v>
+        <v>13279501.51514058</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370117101768</v>
+        <v>987.0883260129439</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370117101768</v>
+        <v>987.0883260129439</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23186206.48727729</v>
+        <v>23185331.97618607</v>
       </c>
     </row>
   </sheetData>
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.34732203575993</v>
+        <v>1.415908396047757</v>
       </c>
       <c r="H2" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -702,16 +702,16 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.798687867826661</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966162046</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>115.5315590288409</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -751,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -781,16 +781,16 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S3" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T3" t="n">
-        <v>4.473444462796863</v>
+        <v>254.1925263074126</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4">
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N4" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O4" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.50414770182039</v>
+        <v>87.36594612241093</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -982,16 +982,16 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S6" t="n">
-        <v>62.48881128536601</v>
+        <v>367.1325312446516</v>
       </c>
       <c r="T6" t="n">
-        <v>4.473444462796863</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1036,7 +1036,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>335.4014589646926</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N7" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O7" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>3.81023156784903</v>
+        <v>5.722467174369123</v>
       </c>
       <c r="I8" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>374</v>
+        <v>132.137182206024</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1252,19 +1252,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S9" t="n">
-        <v>369.9586744897344</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T9" t="n">
-        <v>4.473444462796863</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1273,7 +1273,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>374</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N10" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O10" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P10" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q10" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.83504507946603</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H11" t="n">
         <v>72.84688483418068</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T11" t="n">
         <v>259.6218731858503</v>
@@ -1444,25 +1444,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C12" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E12" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
         <v>3.999611346725456</v>
       </c>
       <c r="H12" t="n">
-        <v>325.021973978874</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>180.333570877285</v>
@@ -1498,19 +1498,19 @@
         <v>131.8202263797056</v>
       </c>
       <c r="T12" t="n">
-        <v>81.3753501231742</v>
+        <v>254.9671660051473</v>
       </c>
       <c r="U12" t="n">
         <v>79.16168051490372</v>
       </c>
       <c r="V12" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W12" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>193.8260072180132</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
         <v>78.39139276613435</v>
@@ -1556,13 +1556,13 @@
         <v>10.3217920922054</v>
       </c>
       <c r="M13" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N13" t="n">
         <v>155.2579933044718</v>
       </c>
       <c r="O13" t="n">
-        <v>230.9267936392535</v>
+        <v>231.765039488851</v>
       </c>
       <c r="P13" t="n">
         <v>291.4220612627037</v>
@@ -1620,10 +1620,10 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H14" t="n">
-        <v>73.30747219949504</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1681,25 +1681,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>237.1483725282995</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C15" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>200.5295027796756</v>
       </c>
       <c r="E15" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
         <v>3.99961134672543</v>
       </c>
       <c r="H15" t="n">
-        <v>4.021973978873973</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1744,7 +1744,7 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
         <v>98.86273944538755</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M16" t="n">
         <v>102.3923982877958</v>
@@ -1811,7 +1811,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S16" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1918,25 +1918,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>113.5995101105026</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
-        <v>3.99961134672543</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H18" t="n">
-        <v>4.021973978873973</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R18" t="n">
-        <v>180.333570877285</v>
+        <v>275.2968386499104</v>
       </c>
       <c r="S18" t="n">
         <v>131.8202263797057</v>
@@ -2027,10 +2027,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>9.483546242607703</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M19" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N19" t="n">
         <v>155.2579933044718</v>
@@ -2094,7 +2094,7 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H20" t="n">
-        <v>73.30747219949504</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T20" t="n">
         <v>259.6218731858503</v>
@@ -2164,16 +2164,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>116.6353649945385</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>324.9996113467254</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H21" t="n">
-        <v>4.021973978873973</v>
+        <v>98.9852417514997</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2215,16 +2215,16 @@
         <v>79.16168051490371</v>
       </c>
       <c r="V21" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W21" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y21" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="22">
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M22" t="n">
         <v>102.3923982877958</v>
@@ -2285,7 +2285,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S22" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>142.3350019731772</v>
@@ -2571,7 +2571,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>142.3350019731772</v>
@@ -2632,7 +2632,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>135.063180218145</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D27" t="n">
         <v>26.93768689770263</v>
@@ -2641,13 +2641,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F27" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
         <v>3.999611346725456</v>
       </c>
       <c r="H27" t="n">
-        <v>4.021973978873961</v>
+        <v>98.98524175149976</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2695,7 +2695,7 @@
         <v>432.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
         <v>78.39139276613435</v>
@@ -2802,13 +2802,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H29" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>142.3350019731772</v>
@@ -2869,22 +2869,22 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C30" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>121.9009546703283</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E30" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F30" t="n">
-        <v>339.6362423378769</v>
+        <v>192.22805821985</v>
       </c>
       <c r="G30" t="n">
-        <v>3.99961134672543</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H30" t="n">
-        <v>4.021973978873973</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2911,19 +2911,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S30" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T30" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U30" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V30" t="n">
         <v>93.51066719152016</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M31" t="n">
         <v>102.3923982877958</v>
@@ -2987,13 +2987,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P31" t="n">
-        <v>290.5838154131063</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q31" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S31" t="n">
         <v>30.56285675203577</v>
@@ -3042,7 +3042,7 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H32" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
         <v>328.1106633827815</v>
       </c>
       <c r="V32" t="n">
-        <v>309.3116115321383</v>
+        <v>308.8510241668239</v>
       </c>
       <c r="W32" t="n">
         <v>317.3734759809475</v>
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
         <v>3.99961134672543</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>180.333570877285</v>
+        <v>353.9253867592579</v>
       </c>
       <c r="S33" t="n">
         <v>131.8202263797057</v>
@@ -3172,7 +3172,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y33" t="n">
-        <v>251.9832086481071</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="34">
@@ -3215,7 +3215,7 @@
         <v>10.32179209220538</v>
       </c>
       <c r="M34" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N34" t="n">
         <v>155.2579933044718</v>
@@ -3227,7 +3227,7 @@
         <v>291.4220612627038</v>
       </c>
       <c r="Q34" t="n">
-        <v>352.0570205760006</v>
+        <v>352.895266425598</v>
       </c>
       <c r="R34" t="n">
         <v>377.7099312598395</v>
@@ -3276,13 +3276,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H35" t="n">
-        <v>73.30747219949504</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3340,25 +3340,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>237.1483725282995</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C36" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F36" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H36" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3391,13 +3391,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S36" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T36" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U36" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V36" t="n">
         <v>93.51066719152016</v>
@@ -3406,10 +3406,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>98.86273944538755</v>
+        <v>272.4545553273608</v>
       </c>
       <c r="Y36" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="37">
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M37" t="n">
         <v>102.3923982877958</v>
@@ -3461,16 +3461,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P37" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q37" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S37" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>142.3350019731772</v>
@@ -3586,10 +3586,10 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G39" t="n">
         <v>3.999611346725456</v>
@@ -3640,13 +3640,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>111.3731429098285</v>
+        <v>284.9649587918016</v>
       </c>
       <c r="X39" t="n">
-        <v>272.4545553273606</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y39" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="40">
@@ -3756,7 +3756,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>142.3350019731772</v>
@@ -3814,19 +3814,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C42" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>200.5295027796757</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
         <v>3.999611346725456</v>
@@ -3835,7 +3835,7 @@
         <v>4.021973978873961</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>94.96326777262577</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R42" t="n">
         <v>180.333570877285</v>
@@ -3877,7 +3877,7 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>98.86273944538755</v>
@@ -3944,7 +3944,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S43" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090243887</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -4057,16 +4057,16 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>21.67209722191262</v>
+        <v>195.2639131038855</v>
       </c>
       <c r="F45" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>3.99961134672543</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H45" t="n">
         <v>4.021973978873973</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>180.333570877285</v>
@@ -4111,16 +4111,16 @@
         <v>79.16168051490371</v>
       </c>
       <c r="V45" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>206.3364106824542</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="46">
@@ -4178,10 +4178,10 @@
         <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>377.7099312598395</v>
+        <v>376.871685410242</v>
       </c>
       <c r="S46" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.914147375084</v>
+        <v>104.8416377852017</v>
       </c>
       <c r="C2" t="n">
-        <v>56.9398259175144</v>
+        <v>54.86731632763205</v>
       </c>
       <c r="D2" t="n">
-        <v>46.49623426110047</v>
+        <v>44.42372467121812</v>
       </c>
       <c r="E2" t="n">
-        <v>42.08887102183921</v>
+        <v>40.01636143195687</v>
       </c>
       <c r="F2" t="n">
-        <v>37.14985212485754</v>
+        <v>35.07734253497519</v>
       </c>
       <c r="G2" t="n">
-        <v>33.76871875540306</v>
+        <v>33.64713203391685</v>
       </c>
       <c r="H2" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="I2" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="J2" t="n">
-        <v>400.18</v>
+        <v>399.11</v>
       </c>
       <c r="K2" t="n">
-        <v>633.3261931588676</v>
+        <v>630.1058206463047</v>
       </c>
       <c r="L2" t="n">
-        <v>697.388108133742</v>
+        <v>694.7957936111288</v>
       </c>
       <c r="M2" t="n">
-        <v>1067.648108133742</v>
+        <v>1064.065793611129</v>
       </c>
       <c r="N2" t="n">
-        <v>1067.648108133742</v>
+        <v>1064.065793611129</v>
       </c>
       <c r="O2" t="n">
-        <v>1067.648108133742</v>
+        <v>1064.065793611129</v>
       </c>
       <c r="P2" t="n">
-        <v>1125.74</v>
+        <v>1122.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="R2" t="n">
-        <v>1494.183143567852</v>
+        <v>1492</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.815317606417</v>
+        <v>1405.724707412505</v>
       </c>
       <c r="T2" t="n">
-        <v>1221.067250178448</v>
+        <v>1218.994415731959</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3617021698518</v>
+        <v>967.2891925799695</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1889504861913</v>
+        <v>735.116440896309</v>
       </c>
       <c r="W2" t="n">
-        <v>496.4076616165473</v>
+        <v>494.335152026665</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1835874138526</v>
+        <v>300.1110778239703</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.7417362190987</v>
+        <v>187.6692266292163</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>847.9629120561149</v>
+        <v>592.9069117175475</v>
       </c>
       <c r="C3" t="n">
-        <v>483.2155257475095</v>
+        <v>592.9069117175475</v>
       </c>
       <c r="D3" t="n">
-        <v>366.5169812739328</v>
+        <v>241.454702729969</v>
       </c>
       <c r="E3" t="n">
-        <v>366.5169812739328</v>
+        <v>241.454702729969</v>
       </c>
       <c r="F3" t="n">
-        <v>366.5169812739328</v>
+        <v>241.454702729969</v>
       </c>
       <c r="G3" t="n">
-        <v>366.5169812739328</v>
+        <v>241.454702729969</v>
       </c>
       <c r="H3" t="n">
-        <v>33.13396963146437</v>
+        <v>241.454702729969</v>
       </c>
       <c r="I3" t="n">
-        <v>33.13396963146437</v>
+        <v>29.84</v>
       </c>
       <c r="J3" t="n">
-        <v>177.6113405614803</v>
+        <v>174.5185557413367</v>
       </c>
       <c r="K3" t="n">
-        <v>401.8775591086939</v>
+        <v>399.1286311753428</v>
       </c>
       <c r="L3" t="n">
-        <v>720.3885386284223</v>
+        <v>714.3818833454036</v>
       </c>
       <c r="M3" t="n">
-        <v>861.5031803712816</v>
+        <v>856.0360750882628</v>
       </c>
       <c r="N3" t="n">
-        <v>1051.274153846774</v>
+        <v>1046.360878846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.994549492757</v>
+        <v>1337.587921002191</v>
       </c>
       <c r="P3" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="Q3" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="R3" t="n">
-        <v>1360.997993968056</v>
+        <v>1357.132890099179</v>
       </c>
       <c r="S3" t="n">
-        <v>1297.877982568697</v>
+        <v>1294.053235093949</v>
       </c>
       <c r="T3" t="n">
-        <v>1293.359351798195</v>
+        <v>1037.293107510704</v>
       </c>
       <c r="U3" t="n">
-        <v>1293.161446951808</v>
+        <v>1037.09534560314</v>
       </c>
       <c r="V3" t="n">
-        <v>1278.504207364414</v>
+        <v>1022.438106015746</v>
       </c>
       <c r="W3" t="n">
-        <v>1245.804063011052</v>
+        <v>989.7379616623834</v>
       </c>
       <c r="X3" t="n">
-        <v>1225.740689833893</v>
+        <v>969.6745884852243</v>
       </c>
       <c r="Y3" t="n">
-        <v>847.9629120561149</v>
+        <v>592.9069117175475</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.92</v>
+        <v>216.7176894066534</v>
       </c>
       <c r="C4" t="n">
-        <v>29.92</v>
+        <v>342.7196952250891</v>
       </c>
       <c r="D4" t="n">
-        <v>87.67946781506721</v>
+        <v>456.0388393500892</v>
       </c>
       <c r="E4" t="n">
-        <v>205.5083720264802</v>
+        <v>573.8677435615023</v>
       </c>
       <c r="F4" t="n">
-        <v>329.8693446184157</v>
+        <v>698.2287161534377</v>
       </c>
       <c r="G4" t="n">
-        <v>483.4580055872682</v>
+        <v>851.8191623681919</v>
       </c>
       <c r="H4" t="n">
-        <v>654.5935815663379</v>
+        <v>1022.970610806278</v>
       </c>
       <c r="I4" t="n">
-        <v>881.2025562401257</v>
+        <v>1249.633272693181</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.462556240126</v>
+        <v>1249.633272693181</v>
       </c>
       <c r="K4" t="n">
-        <v>1382.983127881912</v>
+        <v>1381.361257449721</v>
       </c>
       <c r="L4" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="M4" t="n">
-        <v>1294.017231267251</v>
+        <v>1292.946305617309</v>
       </c>
       <c r="N4" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.742122945132</v>
       </c>
       <c r="O4" t="n">
-        <v>932.9209073660642</v>
+        <v>932.3861797621563</v>
       </c>
       <c r="P4" t="n">
-        <v>665.0402361121327</v>
+        <v>664.7258098826245</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3053387456568</v>
       </c>
       <c r="R4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="S4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="T4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="U4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="V4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="W4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="X4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="Y4" t="n">
-        <v>29.92</v>
+        <v>104.9603517403612</v>
       </c>
     </row>
     <row r="5">
@@ -4534,49 +4534,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.731003807232</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C5" t="n">
-        <v>58.7566823496624</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D5" t="n">
-        <v>48.31309069324847</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E5" t="n">
-        <v>43.90572745398721</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F5" t="n">
-        <v>38.96670855700554</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G5" t="n">
-        <v>35.58557518755106</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H5" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>327.1281081337421</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K5" t="n">
-        <v>697.3881081337421</v>
+        <v>400.2796902997726</v>
       </c>
       <c r="L5" t="n">
-        <v>1067.648108133742</v>
+        <v>464.9696632645968</v>
       </c>
       <c r="M5" t="n">
-        <v>1437.908108133742</v>
+        <v>835.2296632645968</v>
       </c>
       <c r="N5" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O5" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P5" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U5" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V5" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W5" t="n">
-        <v>498.2245180486953</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X5" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y5" t="n">
-        <v>191.5585926512467</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>903.8007408899989</v>
+        <v>917.9636424057419</v>
       </c>
       <c r="C6" t="n">
-        <v>903.8007408899989</v>
+        <v>917.9636424057419</v>
       </c>
       <c r="D6" t="n">
-        <v>903.8007408899989</v>
+        <v>917.9636424057419</v>
       </c>
       <c r="E6" t="n">
-        <v>903.8007408899989</v>
+        <v>917.9636424057419</v>
       </c>
       <c r="F6" t="n">
-        <v>903.8007408899989</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="G6" t="n">
-        <v>574.9925190227137</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="H6" t="n">
-        <v>241.6095073802453</v>
+        <v>241.534702729969</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K6" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L6" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M6" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N6" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P6" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1357.784024336592</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S6" t="n">
-        <v>1294.664012937232</v>
+        <v>990.0920348165509</v>
       </c>
       <c r="T6" t="n">
-        <v>1290.14538216673</v>
+        <v>985.5821614312216</v>
       </c>
       <c r="U6" t="n">
-        <v>1289.947477320344</v>
+        <v>985.3843995236573</v>
       </c>
       <c r="V6" t="n">
-        <v>1275.29023773295</v>
+        <v>970.7271599362632</v>
       </c>
       <c r="W6" t="n">
-        <v>1242.590093379587</v>
+        <v>938.0270155829011</v>
       </c>
       <c r="X6" t="n">
-        <v>903.8007408899989</v>
+        <v>917.9636424057419</v>
       </c>
       <c r="Y6" t="n">
-        <v>903.8007408899989</v>
+        <v>917.9636424057419</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>218.6183178716313</v>
+        <v>1250.707100357225</v>
       </c>
       <c r="C7" t="n">
-        <v>344.620323690067</v>
+        <v>1376.709106175661</v>
       </c>
       <c r="D7" t="n">
-        <v>457.9394678150671</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="E7" t="n">
-        <v>575.7683720264802</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="F7" t="n">
-        <v>700.1293446184156</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="G7" t="n">
-        <v>853.7180055872682</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="H7" t="n">
-        <v>1024.853581566338</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="I7" t="n">
-        <v>1251.462556240126</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="J7" t="n">
-        <v>1251.462556240126</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="K7" t="n">
-        <v>1382.983127881912</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M7" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N7" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O7" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P7" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R7" t="n">
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.34367574991084</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T7" t="n">
-        <v>218.6183178716313</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="U7" t="n">
-        <v>218.6183178716313</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="V7" t="n">
-        <v>218.6183178716313</v>
+        <v>704.6187527280301</v>
       </c>
       <c r="W7" t="n">
-        <v>218.6183178716313</v>
+        <v>876.5096709877075</v>
       </c>
       <c r="X7" t="n">
-        <v>218.6183178716313</v>
+        <v>1027.540462011901</v>
       </c>
       <c r="Y7" t="n">
-        <v>218.6183178716313</v>
+        <v>1138.949762690933</v>
       </c>
     </row>
     <row r="8">
@@ -4771,49 +4771,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.731003807232</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C8" t="n">
-        <v>58.7566823496624</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D8" t="n">
-        <v>48.31309069324847</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E8" t="n">
-        <v>43.90572745398721</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F8" t="n">
-        <v>38.96670855700554</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G8" t="n">
-        <v>35.58557518755106</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H8" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>29.92</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K8" t="n">
-        <v>400.18</v>
+        <v>326.5557936111288</v>
       </c>
       <c r="L8" t="n">
-        <v>464.2419149748744</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="M8" t="n">
-        <v>834.5019149748744</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="N8" t="n">
-        <v>1204.761914974874</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="O8" t="n">
-        <v>1204.761914974874</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="P8" t="n">
-        <v>1262.853806841132</v>
+        <v>1496</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4822,25 +4822,25 @@
         <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.632174038565</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.884106610596</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U8" t="n">
-        <v>971.1785586019998</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V8" t="n">
-        <v>739.0058069183393</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W8" t="n">
-        <v>498.2245180486953</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X8" t="n">
-        <v>304.0004438460006</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.5585926512467</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="9">
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.92</v>
+        <v>1092.253026833469</v>
       </c>
       <c r="C9" t="n">
-        <v>29.92</v>
+        <v>727.505640524864</v>
       </c>
       <c r="D9" t="n">
-        <v>29.92</v>
+        <v>376.0534315372855</v>
       </c>
       <c r="E9" t="n">
         <v>29.92</v>
@@ -4874,52 +4874,52 @@
         <v>29.92</v>
       </c>
       <c r="J9" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K9" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L9" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M9" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N9" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P9" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1346.247111942856</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1211.245105910912</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S9" t="n">
-        <v>837.5494751132003</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T9" t="n">
-        <v>833.0308443426984</v>
+        <v>1293.343447077155</v>
       </c>
       <c r="U9" t="n">
-        <v>832.832939496312</v>
+        <v>1293.145685169591</v>
       </c>
       <c r="V9" t="n">
-        <v>818.1756999089179</v>
+        <v>1278.488445582197</v>
       </c>
       <c r="W9" t="n">
-        <v>785.4755555555557</v>
+        <v>1245.788301228835</v>
       </c>
       <c r="X9" t="n">
-        <v>407.6977777777778</v>
+        <v>1225.724928051676</v>
       </c>
       <c r="Y9" t="n">
-        <v>407.6977777777778</v>
+        <v>1225.724928051676</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>431.0883157913439</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="C10" t="n">
-        <v>431.0883157913439</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="D10" t="n">
-        <v>431.0883157913439</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="E10" t="n">
-        <v>431.0883157913439</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="F10" t="n">
-        <v>555.4492883832794</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="G10" t="n">
-        <v>709.0379493521318</v>
+        <v>659.3878060568384</v>
       </c>
       <c r="H10" t="n">
-        <v>880.1735253312015</v>
+        <v>830.5392544949244</v>
       </c>
       <c r="I10" t="n">
-        <v>1106.782500004989</v>
+        <v>1057.201916381827</v>
       </c>
       <c r="J10" t="n">
-        <v>1251.462556240126</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K10" t="n">
-        <v>1382.983127881912</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L10" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M10" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N10" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O10" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P10" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R10" t="n">
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>70.34367574991084</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T10" t="n">
-        <v>259.1973975316665</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="U10" t="n">
-        <v>259.1973975316665</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="V10" t="n">
-        <v>259.1973975316665</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="W10" t="n">
-        <v>431.0883157913439</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="X10" t="n">
-        <v>431.0883157913439</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="Y10" t="n">
-        <v>431.0883157913439</v>
+        <v>505.7973598420842</v>
       </c>
     </row>
     <row r="11">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C11" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D11" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E11" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F11" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G11" t="n">
         <v>125.5027119537179</v>
@@ -5035,13 +5035,13 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K11" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L11" t="n">
-        <v>1418.446838088717</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M11" t="n">
-        <v>1651.83297330616</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N11" t="n">
         <v>1651.83297330616</v>
@@ -5059,25 +5059,25 @@
         <v>2596</v>
       </c>
       <c r="S11" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T11" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U11" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V11" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W11" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X11" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="12">
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1141.180125483445</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C12" t="n">
-        <v>1100.675163417264</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D12" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E12" t="n">
-        <v>727.3319471348246</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F12" t="n">
-        <v>384.2650356824237</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G12" t="n">
-        <v>380.2250242210849</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H12" t="n">
         <v>51.92</v>
@@ -5132,31 +5132,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q12" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R12" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S12" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T12" t="n">
-        <v>1767.260375227614</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U12" t="n">
-        <v>1687.299081778216</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V12" t="n">
-        <v>1592.843862392842</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W12" t="n">
-        <v>1480.3457382415</v>
+        <v>735.9383970570296</v>
       </c>
       <c r="X12" t="n">
-        <v>1284.561892566739</v>
+        <v>636.0770440818907</v>
       </c>
       <c r="Y12" t="n">
-        <v>1205.378667550442</v>
+        <v>556.8938190655933</v>
       </c>
     </row>
     <row r="13">
@@ -5199,10 +5199,10 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M13" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N13" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O13" t="n">
         <v>1115.142339091088</v>
@@ -5263,7 +5263,7 @@
         <v>125.9679517166617</v>
       </c>
       <c r="H14" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I14" t="n">
         <v>51.92</v>
@@ -5272,22 +5272,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K14" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L14" t="n">
-        <v>991.9887866314309</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M14" t="n">
-        <v>1595.767892278425</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N14" t="n">
-        <v>2238.277892278425</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O14" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P14" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q14" t="n">
         <v>2596</v>
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1141.180125483445</v>
+        <v>668.0405455662462</v>
       </c>
       <c r="C15" t="n">
-        <v>776.43273917484</v>
+        <v>627.5355835000652</v>
       </c>
       <c r="D15" t="n">
-        <v>424.9805301872616</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E15" t="n">
         <v>403.0895228924003</v>
       </c>
       <c r="F15" t="n">
-        <v>60.0226114399994</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G15" t="n">
-        <v>55.98259997866058</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H15" t="n">
         <v>51.92</v>
@@ -5387,13 +5387,13 @@
         <v>1672.26663826087</v>
       </c>
       <c r="W15" t="n">
-        <v>1559.768514109528</v>
+        <v>1235.526089867103</v>
       </c>
       <c r="X15" t="n">
-        <v>1459.907161134389</v>
+        <v>1135.664736891964</v>
       </c>
       <c r="Y15" t="n">
-        <v>1380.723936118091</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="16">
@@ -5433,25 +5433,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L16" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M16" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N16" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O16" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P16" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R16" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S16" t="n">
         <v>51.92</v>
@@ -5506,25 +5506,25 @@
         <v>51.92</v>
       </c>
       <c r="J17" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K17" t="n">
-        <v>1201.938527309012</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L17" t="n">
-        <v>1844.448527309012</v>
+        <v>950.0896384907273</v>
       </c>
       <c r="M17" t="n">
-        <v>2238.277892278425</v>
+        <v>1592.599638490728</v>
       </c>
       <c r="N17" t="n">
-        <v>2238.277892278425</v>
+        <v>2235.109638490728</v>
       </c>
       <c r="O17" t="n">
-        <v>2399.40799366138</v>
+        <v>2396.239739873683</v>
       </c>
       <c r="P17" t="n">
-        <v>2596</v>
+        <v>2592.831746212303</v>
       </c>
       <c r="Q17" t="n">
         <v>2596</v>
@@ -5561,22 +5561,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>912.8601939406431</v>
+        <v>1141.180125483446</v>
       </c>
       <c r="C18" t="n">
-        <v>872.355231874462</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D18" t="n">
-        <v>520.9030228868835</v>
+        <v>1073.46537867211</v>
       </c>
       <c r="E18" t="n">
-        <v>174.769591349598</v>
+        <v>1051.574371377249</v>
       </c>
       <c r="F18" t="n">
-        <v>60.0226114399994</v>
+        <v>708.507459924848</v>
       </c>
       <c r="G18" t="n">
-        <v>55.98259997866058</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H18" t="n">
         <v>51.92</v>
@@ -5609,28 +5609,28 @@
         <v>2164.764564500508</v>
       </c>
       <c r="R18" t="n">
-        <v>1982.60944240224</v>
+        <v>1886.686949702618</v>
       </c>
       <c r="S18" t="n">
-        <v>1849.457698584356</v>
+        <v>1753.535205884734</v>
       </c>
       <c r="T18" t="n">
-        <v>1767.260375227614</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U18" t="n">
-        <v>1687.299081778216</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V18" t="n">
-        <v>1592.843862392842</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W18" t="n">
-        <v>1480.3457382415</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X18" t="n">
-        <v>1380.484385266361</v>
+        <v>1284.56189256674</v>
       </c>
       <c r="Y18" t="n">
-        <v>1301.301160250064</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="19">
@@ -5670,7 +5670,7 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L19" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M19" t="n">
         <v>1506.07469544798</v>
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C20" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D20" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E20" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F20" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G20" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H20" t="n">
         <v>51.92</v>
@@ -5746,22 +5746,22 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K20" t="n">
-        <v>1201.938527309012</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L20" t="n">
-        <v>1844.448527309012</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M20" t="n">
-        <v>2238.277892278425</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N20" t="n">
-        <v>2238.277892278425</v>
+        <v>2234.653276253736</v>
       </c>
       <c r="O20" t="n">
-        <v>2399.40799366138</v>
+        <v>2395.783377636692</v>
       </c>
       <c r="P20" t="n">
-        <v>2596</v>
+        <v>2592.375383975311</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
@@ -5770,25 +5770,25 @@
         <v>2596</v>
       </c>
       <c r="S20" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T20" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U20" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V20" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W20" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X20" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="21">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>912.8601939406431</v>
+        <v>264.3753454557945</v>
       </c>
       <c r="C21" t="n">
-        <v>872.355231874462</v>
+        <v>223.8703833896134</v>
       </c>
       <c r="D21" t="n">
-        <v>845.1454471293079</v>
+        <v>196.6605986444592</v>
       </c>
       <c r="E21" t="n">
-        <v>727.3319471348245</v>
+        <v>174.769591349598</v>
       </c>
       <c r="F21" t="n">
-        <v>384.2650356824237</v>
+        <v>155.9451041396213</v>
       </c>
       <c r="G21" t="n">
-        <v>55.98259997866058</v>
+        <v>151.9050926782825</v>
       </c>
       <c r="H21" t="n">
         <v>51.92</v>
@@ -5858,16 +5858,16 @@
         <v>1687.299081778216</v>
       </c>
       <c r="V21" t="n">
-        <v>1592.843862392842</v>
+        <v>1268.601438150418</v>
       </c>
       <c r="W21" t="n">
-        <v>1480.3457382415</v>
+        <v>831.8608897566517</v>
       </c>
       <c r="X21" t="n">
-        <v>1380.484385266361</v>
+        <v>407.7571125390884</v>
       </c>
       <c r="Y21" t="n">
-        <v>977.0587360076396</v>
+        <v>328.5738875227911</v>
       </c>
     </row>
     <row r="22">
@@ -5907,25 +5907,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L22" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M22" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N22" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O22" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P22" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R22" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
@@ -5956,25 +5956,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C23" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D23" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E23" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F23" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G23" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H23" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I23" t="n">
         <v>51.92</v>
@@ -5986,46 +5986,46 @@
         <v>307.5796384907274</v>
       </c>
       <c r="L23" t="n">
-        <v>950.0896384907273</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M23" t="n">
-        <v>1592.599638490728</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N23" t="n">
-        <v>2235.109638490728</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O23" t="n">
-        <v>2396.239739873683</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P23" t="n">
-        <v>2592.831746212303</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
       </c>
       <c r="R23" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S23" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T23" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U23" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V23" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W23" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X23" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="24">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C26" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D26" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E26" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F26" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G26" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H26" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I26" t="n">
         <v>51.92</v>
       </c>
       <c r="J26" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K26" t="n">
-        <v>733.5813277110226</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L26" t="n">
-        <v>1170.453074689115</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M26" t="n">
-        <v>1170.453074689115</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N26" t="n">
-        <v>1170.453074689115</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O26" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P26" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q26" t="n">
         <v>2596</v>
       </c>
       <c r="R26" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S26" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T26" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U26" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V26" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W26" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X26" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="27">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>264.3753454557945</v>
+        <v>588.6177696982188</v>
       </c>
       <c r="C27" t="n">
-        <v>127.9478906899915</v>
+        <v>548.1128076320377</v>
       </c>
       <c r="D27" t="n">
-        <v>100.7381059448373</v>
+        <v>520.9030228868836</v>
       </c>
       <c r="E27" t="n">
-        <v>78.84709864997603</v>
+        <v>499.0120155920224</v>
       </c>
       <c r="F27" t="n">
-        <v>60.02261143999941</v>
+        <v>155.9451041396214</v>
       </c>
       <c r="G27" t="n">
-        <v>55.98259997866057</v>
+        <v>151.9050926782826</v>
       </c>
       <c r="H27" t="n">
         <v>51.92</v>
@@ -6338,10 +6338,10 @@
         <v>831.8608897566517</v>
       </c>
       <c r="X27" t="n">
-        <v>407.7571125390884</v>
+        <v>731.9995367815127</v>
       </c>
       <c r="Y27" t="n">
-        <v>328.5738875227911</v>
+        <v>652.8163117652153</v>
       </c>
     </row>
     <row r="28">
@@ -6430,25 +6430,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C29" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D29" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E29" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F29" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G29" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H29" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I29" t="n">
         <v>51.92</v>
@@ -6457,49 +6457,49 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K29" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L29" t="n">
-        <v>1418.446838088717</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M29" t="n">
-        <v>1595.767892278425</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N29" t="n">
-        <v>2238.277892278425</v>
+        <v>1808.651587033441</v>
       </c>
       <c r="O29" t="n">
-        <v>2399.40799366138</v>
+        <v>1969.781688416396</v>
       </c>
       <c r="P29" t="n">
-        <v>2596</v>
+        <v>2166.373694755016</v>
       </c>
       <c r="Q29" t="n">
         <v>2596</v>
       </c>
       <c r="R29" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S29" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T29" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U29" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V29" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W29" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X29" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="30">
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>912.8601939406431</v>
+        <v>992.2829698086707</v>
       </c>
       <c r="C30" t="n">
-        <v>548.1128076320376</v>
+        <v>951.7780077424896</v>
       </c>
       <c r="D30" t="n">
-        <v>424.9805301872616</v>
+        <v>924.5682229973355</v>
       </c>
       <c r="E30" t="n">
-        <v>403.0895228924003</v>
+        <v>902.6772157024743</v>
       </c>
       <c r="F30" t="n">
-        <v>60.0226114399994</v>
+        <v>708.507459924848</v>
       </c>
       <c r="G30" t="n">
-        <v>55.98259997866058</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6554,31 +6554,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q30" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R30" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S30" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T30" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U30" t="n">
-        <v>1687.299081778216</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V30" t="n">
-        <v>1592.843862392842</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W30" t="n">
-        <v>1480.3457382415</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X30" t="n">
-        <v>1380.484385266361</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y30" t="n">
-        <v>1301.301160250064</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="31">
@@ -6618,22 +6618,22 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L31" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M31" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N31" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O31" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P31" t="n">
         <v>820.7766206439126</v>
       </c>
       <c r="Q31" t="n">
-        <v>464.3167555675508</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R31" t="n">
         <v>82.79157247680381</v>
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C32" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D32" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E32" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F32" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G32" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H32" t="n">
         <v>51.92</v>
@@ -6694,22 +6694,22 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K32" t="n">
-        <v>733.5813277110226</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L32" t="n">
-        <v>949.6332762537361</v>
+        <v>1417.990475851726</v>
       </c>
       <c r="M32" t="n">
-        <v>1592.143276253736</v>
+        <v>2060.500475851726</v>
       </c>
       <c r="N32" t="n">
-        <v>2234.653276253736</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O32" t="n">
-        <v>2395.783377636692</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P32" t="n">
-        <v>2592.375383975311</v>
+        <v>2596</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
@@ -6727,16 +6727,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W32" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X32" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="33">
@@ -6746,16 +6746,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>816.9377012410212</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C33" t="n">
-        <v>452.1903149324157</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D33" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E33" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F33" t="n">
         <v>60.0226114399994</v>
@@ -6794,25 +6794,25 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R33" t="n">
-        <v>2062.032218270268</v>
+        <v>1886.686949702618</v>
       </c>
       <c r="S33" t="n">
-        <v>1928.880474452383</v>
+        <v>1753.535205884734</v>
       </c>
       <c r="T33" t="n">
-        <v>1846.683151095641</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U33" t="n">
-        <v>1766.721857646244</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V33" t="n">
-        <v>1672.26663826087</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W33" t="n">
-        <v>1559.768514109528</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X33" t="n">
-        <v>1459.907161134389</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y33" t="n">
         <v>1205.378667550442</v>
@@ -6858,16 +6858,16 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M34" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N34" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O34" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P34" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q34" t="n">
         <v>464.3167555675508</v>
@@ -6904,25 +6904,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>597.1205880922942</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C35" t="n">
-        <v>467.3482868367447</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D35" t="n">
-        <v>377.106715382351</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E35" t="n">
-        <v>292.9013723451099</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F35" t="n">
-        <v>208.1643736501484</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G35" t="n">
-        <v>125.9679517166617</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H35" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I35" t="n">
         <v>51.92</v>
@@ -6931,13 +6931,13 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K35" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L35" t="n">
-        <v>991.9887866314309</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M35" t="n">
-        <v>1634.498786631431</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N35" t="n">
         <v>1651.83297330616</v>
@@ -6964,16 +6964,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V35" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W35" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X35" t="n">
-        <v>951.9859877270223</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y35" t="n">
-        <v>759.7461567342887</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="36">
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1141.180125483445</v>
+        <v>492.6952769985968</v>
       </c>
       <c r="C36" t="n">
-        <v>776.43273917484</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D36" t="n">
-        <v>424.9805301872615</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E36" t="n">
         <v>78.84709864997603</v>
       </c>
       <c r="F36" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G36" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H36" t="n">
         <v>51.92</v>
@@ -7037,7 +7037,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T36" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U36" t="n">
         <v>1766.721857646244</v>
@@ -7049,10 +7049,10 @@
         <v>1559.768514109528</v>
       </c>
       <c r="X36" t="n">
-        <v>1459.907161134389</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y36" t="n">
-        <v>1380.723936118091</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="37">
@@ -7104,13 +7104,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P37" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q37" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R37" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S37" t="n">
         <v>51.92</v>
@@ -7141,25 +7141,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C38" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D38" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E38" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F38" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G38" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H38" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I38" t="n">
         <v>51.92</v>
@@ -7174,7 +7174,7 @@
         <v>523.631587033441</v>
       </c>
       <c r="M38" t="n">
-        <v>1009.32297330616</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N38" t="n">
         <v>1651.83297330616</v>
@@ -7189,28 +7189,28 @@
         <v>2596</v>
       </c>
       <c r="R38" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S38" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T38" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U38" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V38" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W38" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X38" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y38" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="39">
@@ -7220,16 +7220,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1141.180125483445</v>
+        <v>492.6952769985968</v>
       </c>
       <c r="C39" t="n">
-        <v>776.43273917484</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D39" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E39" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F39" t="n">
         <v>60.02261143999941</v>
@@ -7283,13 +7283,13 @@
         <v>1672.26663826087</v>
       </c>
       <c r="W39" t="n">
-        <v>1559.768514109528</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X39" t="n">
-        <v>1284.561892566739</v>
+        <v>960.3194683243149</v>
       </c>
       <c r="Y39" t="n">
-        <v>1205.378667550442</v>
+        <v>556.8938190655933</v>
       </c>
     </row>
     <row r="40">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C41" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D41" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E41" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F41" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G41" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H41" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I41" t="n">
         <v>51.92</v>
       </c>
       <c r="J41" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K41" t="n">
-        <v>1201.938527309012</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L41" t="n">
-        <v>1417.990475851726</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M41" t="n">
-        <v>2060.500475851726</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N41" t="n">
-        <v>2060.500475851726</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O41" t="n">
-        <v>2221.630577234681</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P41" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q41" t="n">
         <v>2596</v>
       </c>
       <c r="R41" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S41" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T41" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U41" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W41" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X41" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1316.525394051095</v>
+        <v>588.6177696982188</v>
       </c>
       <c r="C42" t="n">
-        <v>951.7780077424895</v>
+        <v>223.8703833896134</v>
       </c>
       <c r="D42" t="n">
-        <v>749.2229544296858</v>
+        <v>196.6605986444593</v>
       </c>
       <c r="E42" t="n">
-        <v>403.0895228924003</v>
+        <v>174.769591349598</v>
       </c>
       <c r="F42" t="n">
-        <v>60.02261143999941</v>
+        <v>155.9451041396214</v>
       </c>
       <c r="G42" t="n">
-        <v>55.98259997866057</v>
+        <v>151.9050926782826</v>
       </c>
       <c r="H42" t="n">
-        <v>51.92</v>
+        <v>147.842492699622</v>
       </c>
       <c r="I42" t="n">
         <v>51.92</v>
@@ -7502,31 +7502,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q42" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R42" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S42" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T42" t="n">
-        <v>1846.683151095642</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U42" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V42" t="n">
-        <v>1672.26663826087</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W42" t="n">
-        <v>1559.768514109528</v>
+        <v>1156.103313999076</v>
       </c>
       <c r="X42" t="n">
-        <v>1459.907161134389</v>
+        <v>1056.241961023937</v>
       </c>
       <c r="Y42" t="n">
-        <v>1380.723936118092</v>
+        <v>977.0587360076396</v>
       </c>
     </row>
     <row r="43">
@@ -7548,10 +7548,10 @@
         <v>809.1641510572457</v>
       </c>
       <c r="F43" t="n">
-        <v>855.3151236491811</v>
+        <v>855.3151236491813</v>
       </c>
       <c r="G43" t="n">
-        <v>931.1258141262304</v>
+        <v>931.1258141262305</v>
       </c>
       <c r="H43" t="n">
         <v>1027.892525187267</v>
@@ -7563,13 +7563,13 @@
         <v>1515.576154611867</v>
       </c>
       <c r="K43" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.080700024146</v>
       </c>
       <c r="L43" t="n">
         <v>1608.654647405756</v>
       </c>
       <c r="M43" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.227982468589</v>
       </c>
       <c r="N43" t="n">
         <v>1348.401726605486</v>
@@ -7578,13 +7578,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P43" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645217</v>
       </c>
       <c r="Q43" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881601</v>
       </c>
       <c r="R43" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949741301</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7639,25 +7639,25 @@
         <v>51.92</v>
       </c>
       <c r="J44" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K44" t="n">
-        <v>1201.938527309012</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L44" t="n">
-        <v>1595.767892278425</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M44" t="n">
-        <v>2238.277892278425</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N44" t="n">
-        <v>2238.277892278425</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O44" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P44" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q44" t="n">
         <v>2596</v>
@@ -7694,19 +7694,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>168.4528527561725</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C45" t="n">
-        <v>127.9478906899915</v>
+        <v>1276.020431984914</v>
       </c>
       <c r="D45" t="n">
-        <v>100.7381059448373</v>
+        <v>924.5682229973352</v>
       </c>
       <c r="E45" t="n">
-        <v>78.84709864997603</v>
+        <v>727.3319471348245</v>
       </c>
       <c r="F45" t="n">
-        <v>60.0226114399994</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G45" t="n">
         <v>55.98259997866058</v>
@@ -7739,31 +7739,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q45" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R45" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S45" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T45" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U45" t="n">
-        <v>1687.299081778216</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V45" t="n">
-        <v>1268.601438150418</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W45" t="n">
-        <v>1060.180821299454</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X45" t="n">
-        <v>636.0770440818908</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y45" t="n">
-        <v>232.6513948231691</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="46">
@@ -7821,7 +7821,7 @@
         <v>463.4700425881595</v>
       </c>
       <c r="R46" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S46" t="n">
         <v>51.92</v>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>374.2405037325275</v>
+        <v>372.8993027275024</v>
       </c>
       <c r="K2" t="n">
-        <v>183.3412755627362</v>
+        <v>180.6578102564064</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>846.2608914614127</v>
+        <v>844.554996989051</v>
       </c>
       <c r="N2" t="n">
-        <v>404.0826666125488</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O2" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>502.5418702571336</v>
+        <v>501.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8049,7 +8049,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L3" t="n">
-        <v>388.0893364597981</v>
+        <v>384.3316744713784</v>
       </c>
       <c r="M3" t="n">
         <v>471.6948204301074</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>300.4507139686307</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L5" t="n">
-        <v>309.2909949748744</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>846.2608914614127</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N5" t="n">
-        <v>404.0826666125488</v>
+        <v>637.5533604806767</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>128.5418702571336</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2405037325275146</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>321.8400703517588</v>
+        <v>246.8601159786807</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>308.6565929648241</v>
       </c>
       <c r="M8" t="n">
-        <v>846.2608914614127</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N8" t="n">
-        <v>778.0826666125488</v>
+        <v>777.3653500296342</v>
       </c>
       <c r="O8" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>364.0430754681111</v>
+        <v>128.1077446289929</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,16 +8678,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>537.1780000765643</v>
+        <v>792.031789021288</v>
       </c>
       <c r="N11" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8915,16 +8915,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>911.3123136417682</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N14" t="n">
-        <v>879.4920535472222</v>
+        <v>721.0894134186553</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>473.08808040201</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M17" t="n">
-        <v>699.241868512898</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N17" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>23.48346824708341</v>
+        <v>26.68372459829277</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,16 +9389,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>473.08808040201</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>699.241868512898</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N20" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>23.48346824708341</v>
+        <v>27.14469655484982</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>950.4344291498551</v>
+        <v>792.031789021288</v>
       </c>
       <c r="N23" t="n">
         <v>879.4920535472222</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>26.68372459829277</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,28 +9860,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L26" t="n">
-        <v>223.0503014498773</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N26" t="n">
-        <v>230.4920535472222</v>
+        <v>840.3699380391354</v>
       </c>
       <c r="O26" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,13 +10100,13 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>480.5466050990546</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N29" t="n">
         <v>879.4920535472222</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>23.48346824708341</v>
+        <v>457.4494331410071</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,7 +10337,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -10346,7 +10346,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N32" t="n">
-        <v>879.4920535472222</v>
+        <v>410.0652014529786</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>27.14469655484982</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,7 +10574,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -10583,7 +10583,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N35" t="n">
-        <v>248.0013330166451</v>
+        <v>721.0894134186553</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10817,10 +10817,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>792.031789021288</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N38" t="n">
-        <v>879.4920535472222</v>
+        <v>721.0894134186553</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -11045,10 +11045,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>473.08808040201</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -11057,16 +11057,16 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N41" t="n">
-        <v>230.4920535472222</v>
+        <v>721.0894134186553</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>179.5731479057563</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,19 +11282,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>473.08808040201</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L44" t="n">
-        <v>179.5731479057567</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N44" t="n">
-        <v>230.4920535472222</v>
+        <v>248.0013330166451</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.927393539209687</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -23414,13 +23414,13 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -23648,7 +23648,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23885,10 +23885,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -24122,7 +24122,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>0.8382458495976959</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -24845,7 +24845,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -25073,7 +25073,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -25085,7 +25085,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -25328,7 +25328,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495968947</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26036,10 +26036,10 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="S46" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>892178.9310546662</v>
+        <v>891890.0617539416</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1710774.007270852</v>
+        <v>1710591.902429133</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2529369.083487039</v>
+        <v>2529186.978645321</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3347516.760067973</v>
+        <v>3347417.036726255</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4166098.759648907</v>
+        <v>4165999.036307188</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4984680.759229839</v>
+        <v>4984581.035888121</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5803262.758810768</v>
+        <v>5803163.03546905</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6621844.758391697</v>
+        <v>6621745.035049979</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7440426.757972627</v>
+        <v>7440327.034630908</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8259008.757553556</v>
+        <v>8258909.034211838</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9077590.757134493</v>
+        <v>9077491.033792775</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9896172.756715432</v>
+        <v>9896073.033373713</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10714754.75629637</v>
+        <v>10714655.03295465</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11533336.75587731</v>
+        <v>11533237.03253559</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12351918.75545825</v>
+        <v>12351819.03211653</v>
       </c>
     </row>
   </sheetData>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1385314.744365854</v>
+        <v>1385145.981787561</v>
       </c>
       <c r="C2" t="n">
         <v>1385314.744365854</v>
@@ -26278,7 +26278,7 @@
         <v>1385314.744365854</v>
       </c>
       <c r="E2" t="n">
-        <v>1385292.614675425</v>
+        <v>1385292.614675426</v>
       </c>
       <c r="F2" t="n">
         <v>1385292.614675425</v>
@@ -26290,10 +26290,10 @@
         <v>1385292.614675425</v>
       </c>
       <c r="I2" t="n">
+        <v>1385292.614675426</v>
+      </c>
+      <c r="J2" t="n">
         <v>1385292.614675425</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1385292.614675426</v>
       </c>
       <c r="K2" t="n">
         <v>1385292.614675425</v>
@@ -26321,16 +26321,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231098</v>
+        <v>231721</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>589550</v>
+        <v>588575</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,10 +26345,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388448</v>
+        <v>388096</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667652</v>
+        <v>570823.1065049332</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568738.1032495913</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634526</v>
+        <v>566727.0147207876</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.9797961749</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779522</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259448</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463363</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457892</v>
+        <v>476717.7102154349</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308644</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216767</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589555</v>
+        <v>468216.2325286013</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604933</v>
+        <v>466508.609930139</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26425,13 +26425,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58590.39999999999</v>
+        <v>58551.39999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="D5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="E5" t="n">
         <v>73944.549</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>518161.4096990888</v>
+        <v>524050.4752826277</v>
       </c>
       <c r="C6" t="n">
-        <v>751268.3318865778</v>
+        <v>757612.4411162632</v>
       </c>
       <c r="D6" t="n">
-        <v>753279.9793024015</v>
+        <v>759975.5296450668</v>
       </c>
       <c r="E6" t="n">
-        <v>231859.0858792501</v>
+        <v>239297.077009605</v>
       </c>
       <c r="F6" t="n">
-        <v>823095.1486974728</v>
+        <v>829558.1398278276</v>
       </c>
       <c r="G6" t="n">
-        <v>824783.5382191262</v>
+        <v>831246.5293494797</v>
       </c>
       <c r="H6" t="n">
-        <v>826474.2711290886</v>
+        <v>832937.2622594433</v>
       </c>
       <c r="I6" t="n">
-        <v>828167.3643296362</v>
+        <v>834630.3554599908</v>
       </c>
       <c r="J6" t="n">
-        <v>441414.8349445618</v>
+        <v>448229.826074915</v>
       </c>
       <c r="K6" t="n">
-        <v>831560.7003233939</v>
+        <v>837671.6914537485</v>
       </c>
       <c r="L6" t="n">
-        <v>833260.9780457382</v>
+        <v>839723.9691760924</v>
       </c>
       <c r="M6" t="n">
-        <v>738163.6859257062</v>
+        <v>744626.6770560603</v>
       </c>
       <c r="N6" t="n">
-        <v>836668.8420164703</v>
+        <v>843131.8331468244</v>
       </c>
       <c r="O6" t="n">
-        <v>581576.4646149321</v>
+        <v>588039.4557452864</v>
       </c>
       <c r="P6" t="n">
-        <v>840086.5722665153</v>
+        <v>846549.5633968696</v>
       </c>
     </row>
   </sheetData>
@@ -26807,13 +26807,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" t="n">
         <v>344</v>
@@ -26859,7 +26859,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="n">
         <v>374</v>
@@ -26999,16 +26999,16 @@
         <v>321</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>-0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27033,7 +27033,7 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27076,10 +27076,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>-0</v>
@@ -27100,10 +27100,10 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
@@ -27317,10 +27317,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.2726973711268</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>223.3220918649904</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>399.999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27515,10 +27515,10 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>232.4061278688617</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
@@ -27527,13 +27527,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27566,7 +27566,7 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>150.2722483440635</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>25.39139276613435</v>
+        <v>26.39139276613435</v>
       </c>
     </row>
     <row r="4">
@@ -27591,13 +27591,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>343.8791148384516</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27615,7 +27615,7 @@
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>396.2647849014816</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
@@ -27642,13 +27642,13 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1680042930194</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T4" t="n">
-        <v>209.2386648669134</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9483584875727</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27660,7 +27660,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>363.3444960215444</v>
       </c>
     </row>
     <row r="5">
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>132.4740095033003</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,10 +27718,10 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>398.0465935392085</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27761,10 +27761,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -27794,13 +27794,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>400</v>
+        <v>95.31632721052574</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27815,7 +27815,7 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>84.46128048069494</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27828,37 +27828,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
         <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>294.3826718271959</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>244.858135136612</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J7" t="n">
-        <v>22.26478490148153</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L7" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27882,22 +27882,22 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>359.011030646429</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27925,10 +27925,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>400</v>
+        <v>398.0465935392086</v>
       </c>
       <c r="I8" t="n">
-        <v>132.4740095033003</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27986,28 +27986,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10.55655664632661</v>
+        <v>252.4193744403026</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>92.53013679563151</v>
+        <v>400</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
@@ -28052,7 +28052,7 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>45.86273944538755</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28077,7 +28077,7 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
         <v>400</v>
@@ -28089,7 +28089,7 @@
         <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>168.4062558460637</v>
+        <v>216.5932085642164</v>
       </c>
       <c r="K10" t="n">
         <v>400</v>
@@ -28122,13 +28122,13 @@
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
         <v>247.4436454301076</v>
@@ -28159,7 +28159,7 @@
         <v>321</v>
       </c>
       <c r="G11" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="H11" t="n">
         <v>321</v>
@@ -28195,7 +28195,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S11" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T11" t="n">
         <v>321</v>
@@ -28223,25 +28223,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>321</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E12" t="n">
         <v>321</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G12" t="n">
         <v>321</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I12" t="n">
         <v>191.6509141932353</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R12" t="n">
         <v>321</v>
@@ -28277,19 +28277,19 @@
         <v>321</v>
       </c>
       <c r="T12" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="U12" t="n">
         <v>321</v>
       </c>
       <c r="V12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>226.0367322273743</v>
+        <v>321</v>
       </c>
       <c r="Y12" t="n">
         <v>321</v>
@@ -28399,10 +28399,10 @@
         <v>321</v>
       </c>
       <c r="H14" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="I14" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28460,25 +28460,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>147.4081841180271</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>147.408184118027</v>
       </c>
       <c r="E15" t="n">
         <v>321</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G15" t="n">
         <v>321</v>
       </c>
       <c r="H15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>191.6509141932353</v>
@@ -28523,7 +28523,7 @@
         <v>321</v>
       </c>
       <c r="W15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>321</v>
@@ -28697,25 +28697,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C18" t="n">
         <v>321</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F18" t="n">
-        <v>226.0367322273743</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>191.6509141932353</v>
@@ -28745,7 +28745,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>321</v>
+        <v>226.0367322273746</v>
       </c>
       <c r="S18" t="n">
         <v>321</v>
@@ -28873,7 +28873,7 @@
         <v>321</v>
       </c>
       <c r="H20" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="I20" t="n">
         <v>96.76634561233286</v>
@@ -28906,7 +28906,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S20" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T20" t="n">
         <v>321</v>
@@ -28943,16 +28943,16 @@
         <v>321</v>
       </c>
       <c r="E21" t="n">
-        <v>226.0367322273741</v>
+        <v>321</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H21" t="n">
-        <v>321</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="I21" t="n">
         <v>191.6509141932353</v>
@@ -28994,16 +28994,16 @@
         <v>321</v>
       </c>
       <c r="V21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="22">
@@ -29113,7 +29113,7 @@
         <v>321</v>
       </c>
       <c r="I23" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S23" t="n">
         <v>321</v>
@@ -29350,7 +29350,7 @@
         <v>321</v>
       </c>
       <c r="I26" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29411,7 +29411,7 @@
         <v>321</v>
       </c>
       <c r="C27" t="n">
-        <v>226.0367322273743</v>
+        <v>321</v>
       </c>
       <c r="D27" t="n">
         <v>321</v>
@@ -29420,13 +29420,13 @@
         <v>321</v>
       </c>
       <c r="F27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>321</v>
       </c>
       <c r="H27" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="I27" t="n">
         <v>191.6509141932353</v>
@@ -29474,7 +29474,7 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y27" t="n">
         <v>321</v>
@@ -29587,7 +29587,7 @@
         <v>321</v>
       </c>
       <c r="I29" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29648,22 +29648,22 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D30" t="n">
-        <v>226.0367322273744</v>
+        <v>321</v>
       </c>
       <c r="E30" t="n">
         <v>321</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="G30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>191.6509141932353</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R30" t="n">
         <v>321</v>
@@ -29821,7 +29821,7 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I32" t="n">
         <v>96.76634561233286</v>
@@ -29863,7 +29863,7 @@
         <v>321</v>
       </c>
       <c r="V32" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="W32" t="n">
         <v>321</v>
@@ -29882,19 +29882,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>321</v>
@@ -29930,7 +29930,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R33" t="n">
-        <v>321</v>
+        <v>147.408184118027</v>
       </c>
       <c r="S33" t="n">
         <v>321</v>
@@ -29951,7 +29951,7 @@
         <v>321</v>
       </c>
       <c r="Y33" t="n">
-        <v>147.4081841180273</v>
+        <v>321</v>
       </c>
     </row>
     <row r="34">
@@ -30058,10 +30058,10 @@
         <v>321</v>
       </c>
       <c r="H35" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="I35" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30119,16 +30119,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>147.4081841180271</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F36" t="n">
         <v>321</v>
@@ -30185,10 +30185,10 @@
         <v>321</v>
       </c>
       <c r="X36" t="n">
-        <v>321</v>
+        <v>147.4081841180267</v>
       </c>
       <c r="Y36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -30298,7 +30298,7 @@
         <v>321</v>
       </c>
       <c r="I38" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S38" t="n">
         <v>321</v>
@@ -30365,10 +30365,10 @@
         <v>321</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G39" t="n">
         <v>321</v>
@@ -30419,13 +30419,13 @@
         <v>321</v>
       </c>
       <c r="W39" t="n">
-        <v>321</v>
+        <v>147.408184118027</v>
       </c>
       <c r="X39" t="n">
-        <v>147.4081841180269</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -30535,7 +30535,7 @@
         <v>321</v>
       </c>
       <c r="I41" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S41" t="n">
         <v>321</v>
@@ -30593,19 +30593,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G42" t="n">
         <v>321</v>
@@ -30614,7 +30614,7 @@
         <v>321</v>
       </c>
       <c r="I42" t="n">
-        <v>191.6509141932353</v>
+        <v>96.68764642060955</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30638,7 +30638,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>321</v>
@@ -30656,7 +30656,7 @@
         <v>321</v>
       </c>
       <c r="W42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>321</v>
@@ -30836,16 +30836,16 @@
         <v>321</v>
       </c>
       <c r="D45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="F45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>321</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R45" t="n">
         <v>321</v>
@@ -30890,16 +30890,16 @@
         <v>321</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W45" t="n">
-        <v>226.0367322273743</v>
+        <v>321</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="46">
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H2" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I2" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J2" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K2" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M2" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N2" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O2" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P2" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R2" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S2" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T2" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H3" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I3" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K3" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L3" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M3" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O3" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P3" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R3" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S3" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H4" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I4" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J4" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K4" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L4" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M4" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N4" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O4" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P4" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R4" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S4" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H5" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I5" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J5" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K5" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M5" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N5" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O5" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P5" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R5" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S5" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T5" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H6" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I6" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J6" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K6" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L6" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M6" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O6" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P6" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R6" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S6" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H7" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I7" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J7" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K7" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L7" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M7" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N7" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O7" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P7" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R7" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S7" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31565,49 +31565,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H8" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I8" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J8" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K8" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M8" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N8" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O8" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P8" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R8" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S8" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T8" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31644,49 +31644,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H9" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I9" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J9" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K9" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L9" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M9" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O9" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P9" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R9" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S9" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,49 +31723,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H10" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I10" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J10" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K10" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L10" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M10" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N10" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O10" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P10" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R10" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S10" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T10" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -34743,16 +34743,16 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K2" t="n">
-        <v>235.5012052109774</v>
+        <v>233.3291117639441</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M2" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -34761,10 +34761,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K3" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L3" t="n">
-        <v>321.7282621411399</v>
+        <v>318.4376284546069</v>
       </c>
       <c r="M3" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O3" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P3" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34877,13 +34877,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>58.34289678289618</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34892,22 +34892,22 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>155.1400615846995</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H4" t="n">
-        <v>172.8642181606765</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I4" t="n">
-        <v>228.8979542159473</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>132.8490622644307</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L4" t="n">
-        <v>3.798404629106074</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34946,7 +34946,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>75.87914317208205</v>
       </c>
     </row>
     <row r="5">
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>300.2102102361031</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K5" t="n">
         <v>374</v>
       </c>
       <c r="L5" t="n">
-        <v>374</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M5" t="n">
         <v>374</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>234.1880104510425</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K6" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L6" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M6" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O6" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P6" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35114,37 +35114,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>8.846453771640441</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.83199570698065</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T7" t="n">
-        <v>149.7723657795156</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35217,13 +35217,13 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K8" t="n">
+        <v>299.5314174862184</v>
+      </c>
+      <c r="L8" t="n">
         <v>374</v>
-      </c>
-      <c r="L8" t="n">
-        <v>64.70900502512563</v>
       </c>
       <c r="M8" t="n">
         <v>374</v>
@@ -35235,10 +35235,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
-        <v>235.5012052109774</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35296,25 +35296,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K9" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L9" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M9" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O9" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P9" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35363,25 +35363,25 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>155.1400615846995</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H10" t="n">
-        <v>172.8642181606765</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I10" t="n">
-        <v>228.8979542159473</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J10" t="n">
-        <v>146.1414709445822</v>
+        <v>194.4559154660136</v>
       </c>
       <c r="K10" t="n">
-        <v>132.8490622644307</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L10" t="n">
-        <v>3.798404629106074</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,19 +35402,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.83199570698065</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7613351330866</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -35457,16 +35457,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K11" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L11" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M11" t="n">
+        <v>490.597359871433</v>
+      </c>
+      <c r="N11" t="n">
         <v>649</v>
-      </c>
-      <c r="L11" t="n">
-        <v>649</v>
-      </c>
-      <c r="M11" t="n">
-        <v>235.7435709267093</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>162.757678164601</v>
@@ -35694,16 +35694,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K14" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L14" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M14" t="n">
-        <v>609.8778844919133</v>
+        <v>649</v>
       </c>
       <c r="N14" t="n">
-        <v>649</v>
+        <v>490.5973598714331</v>
       </c>
       <c r="O14" t="n">
         <v>162.757678164601</v>
@@ -35712,7 +35712,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K17" t="n">
-        <v>648.9999999999999</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L17" t="n">
         <v>649</v>
       </c>
       <c r="M17" t="n">
-        <v>397.807439363043</v>
+        <v>649</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O17" t="n">
         <v>162.757678164601</v>
@@ -35949,7 +35949,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.200256351209361</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36168,16 +36168,16 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K20" t="n">
-        <v>648.9999999999999</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L20" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M20" t="n">
         <v>649</v>
       </c>
-      <c r="M20" t="n">
-        <v>397.807439363043</v>
-      </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O20" t="n">
         <v>162.757678164601</v>
@@ -36186,7 +36186,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.661228307766413</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36408,10 +36408,10 @@
         <v>175.9119195979899</v>
       </c>
       <c r="L23" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M23" t="n">
-        <v>649</v>
+        <v>490.597359871433</v>
       </c>
       <c r="N23" t="n">
         <v>649</v>
@@ -36423,7 +36423,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.200256351209361</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36639,28 +36639,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K26" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L26" t="n">
-        <v>441.2845929071638</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="O26" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P26" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q26" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36879,13 +36879,13 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K29" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L29" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M29" t="n">
         <v>649</v>
-      </c>
-      <c r="L29" t="n">
-        <v>649</v>
-      </c>
-      <c r="M29" t="n">
-        <v>179.1121759491996</v>
       </c>
       <c r="N29" t="n">
         <v>649</v>
@@ -36897,7 +36897,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>433.9659648939237</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37028,7 +37028,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H31" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I31" t="n">
         <v>163.0214951995539</v>
@@ -37116,7 +37116,7 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K32" t="n">
-        <v>175.9119195979899</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L32" t="n">
         <v>218.2342914572864</v>
@@ -37125,7 +37125,7 @@
         <v>649</v>
       </c>
       <c r="N32" t="n">
-        <v>649</v>
+        <v>179.5731479057565</v>
       </c>
       <c r="O32" t="n">
         <v>162.757678164601</v>
@@ -37134,7 +37134,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.661228307766413</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37353,7 +37353,7 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K35" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L35" t="n">
         <v>218.2342914572864</v>
@@ -37362,7 +37362,7 @@
         <v>649</v>
       </c>
       <c r="N35" t="n">
-        <v>17.50927946942293</v>
+        <v>490.5973598714331</v>
       </c>
       <c r="O35" t="n">
         <v>162.757678164601</v>
@@ -37502,7 +37502,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H37" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I37" t="n">
         <v>163.0214951995539</v>
@@ -37553,7 +37553,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y37" t="n">
-        <v>33.53464715053764</v>
+        <v>33.53464715053765</v>
       </c>
     </row>
     <row r="38">
@@ -37596,10 +37596,10 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M38" t="n">
-        <v>490.597359871433</v>
+        <v>649</v>
       </c>
       <c r="N38" t="n">
-        <v>649</v>
+        <v>490.5973598714331</v>
       </c>
       <c r="O38" t="n">
         <v>162.757678164601</v>
@@ -37824,10 +37824,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K41" t="n">
-        <v>648.9999999999999</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L41" t="n">
         <v>218.2342914572864</v>
@@ -37836,16 +37836,16 @@
         <v>649</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>490.5973598714331</v>
       </c>
       <c r="O41" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P41" t="n">
-        <v>378.1509320861804</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37970,7 +37970,7 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F43" t="n">
-        <v>46.61714403225807</v>
+        <v>46.61714403225808</v>
       </c>
       <c r="G43" t="n">
         <v>76.57645502732242</v>
@@ -38061,19 +38061,19 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K44" t="n">
-        <v>648.9999999999999</v>
+        <v>649</v>
       </c>
       <c r="L44" t="n">
-        <v>397.8074393630432</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M44" t="n">
         <v>649</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>17.50927946942293</v>
       </c>
       <c r="O44" t="n">
         <v>162.757678164601</v>
@@ -38082,7 +38082,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
